--- a/Sample_run/1/student/manhcdhe176818/TC6/GradeDetail.xlsx
+++ b/Sample_run/1/student/manhcdhe176818/TC6/GradeDetail.xlsx
@@ -204,12 +204,6 @@
   </x:si>
   <x:si>
     <x:t>Client closing connection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
   </x:si>
   <x:si>
     <x:t>S111</x:t>
@@ -242,7 +236,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -257,11 +251,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -284,7 +273,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -297,11 +286,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -315,10 +301,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -991,7 +973,7 @@
     <x:col min="8" max="8" width="143.853482" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
-    <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
@@ -1104,7 +1086,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35934</x:v>
+        <x:v>41708</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1163,7 +1145,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>35934</x:v>
+        <x:v>41708</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>48</x:v>
@@ -1216,7 +1198,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35934</x:v>
+        <x:v>41708</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1272,7 +1254,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35934</x:v>
+        <x:v>41708</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1331,7 +1313,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35934</x:v>
+        <x:v>41708</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
         <x:v>48</x:v>
@@ -1387,7 +1369,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>35934</x:v>
+        <x:v>41708</x:v>
       </x:c>
       <x:c r="R7" s="2" t="s">
         <x:v>48</x:v>
@@ -1440,7 +1422,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>35934</x:v>
+        <x:v>41708</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1499,7 +1481,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>35934</x:v>
+        <x:v>41708</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>60</x:v>
@@ -1543,22 +1525,22 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
+        <x:v>41708</x:v>
+      </x:c>
+      <x:c r="Q10" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="Q10" s="0">
-        <x:v>35934</x:v>
-      </x:c>
-      <x:c r="R10" s="2" t="s">
-        <x:v>48</x:v>
+      <x:c r="R10" s="3" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1608,7 +1590,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>35934</x:v>
+        <x:v>41708</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1649,28 +1631,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R12" s="4" t="s">
-        <x:v>63</x:v>
+      <x:c r="P12" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q12" s="0">
+        <x:v>41708</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1720,7 +1702,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P13" s="0">
-        <x:v>54204</x:v>
+        <x:v>51078</x:v>
       </x:c>
       <x:c r="Q13" s="0">
         <x:v>4000</x:v>
@@ -1779,7 +1761,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q14" s="0">
-        <x:v>54204</x:v>
+        <x:v>51078</x:v>
       </x:c>
       <x:c r="R14" s="2" t="s">
         <x:v>48</x:v>
@@ -1832,7 +1814,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P15" s="0">
-        <x:v>54204</x:v>
+        <x:v>51078</x:v>
       </x:c>
       <x:c r="Q15" s="0">
         <x:v>4000</x:v>
@@ -1864,7 +1846,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>46</x:v>
@@ -1885,10 +1867,10 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="O16" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="P16" s="0">
-        <x:v>54204</x:v>
+        <x:v>51078</x:v>
       </x:c>
       <x:c r="Q16" s="0">
         <x:v>4000</x:v>
@@ -1947,7 +1929,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q17" s="0">
-        <x:v>54204</x:v>
+        <x:v>51078</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
         <x:v>48</x:v>
@@ -1976,7 +1958,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
         <x:v>47</x:v>
@@ -1997,13 +1979,13 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="O18" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="P18" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q18" s="0">
-        <x:v>54204</x:v>
+        <x:v>51078</x:v>
       </x:c>
       <x:c r="R18" s="2" t="s">
         <x:v>48</x:v>
@@ -2056,7 +2038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P19" s="0">
-        <x:v>54204</x:v>
+        <x:v>51078</x:v>
       </x:c>
       <x:c r="Q19" s="0">
         <x:v>4000</x:v>
@@ -2115,7 +2097,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q20" s="0">
-        <x:v>54204</x:v>
+        <x:v>51078</x:v>
       </x:c>
       <x:c r="R20" s="3" t="s">
         <x:v>60</x:v>
@@ -2168,7 +2150,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P21" s="0">
-        <x:v>54204</x:v>
+        <x:v>51078</x:v>
       </x:c>
       <x:c r="Q21" s="0">
         <x:v>4000</x:v>
@@ -2224,7 +2206,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P22" s="0">
-        <x:v>54204</x:v>
+        <x:v>51078</x:v>
       </x:c>
       <x:c r="Q22" s="0">
         <x:v>4000</x:v>
@@ -2283,7 +2265,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q23" s="0">
-        <x:v>54204</x:v>
+        <x:v>51078</x:v>
       </x:c>
       <x:c r="R23" s="3" t="s">
         <x:v>60</x:v>
